--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ90"/>
+  <dimension ref="A1:AZ97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2511,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132218114</v>
+        <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>84198</v>
+        <v>92817</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2522,37 +2522,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1444</v>
+        <v>1339</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>707052</v>
+        <v>707274</v>
       </c>
       <c r="R18" t="n">
-        <v>6635913</v>
+        <v>6635576</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2576,12 +2576,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2596,66 +2606,69 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132218114</t>
+          <t>https://artportalen.se/Sighting/137238304</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112801254</v>
+        <v>132218114</v>
       </c>
       <c r="B19" t="n">
-        <v>87322</v>
+        <v>84198</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1988</v>
+        <v>1444</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kryddspindling</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cortinarius percomis</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>707295</v>
+        <v>707052</v>
       </c>
       <c r="R19" t="n">
-        <v>6635639</v>
+        <v>6635913</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2679,22 +2692,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:10</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2714,19 +2717,19 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801254</t>
+          <t>https://artportalen.se/Sighting/132218114</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113024358</v>
+        <v>112801254</v>
       </c>
       <c r="B20" t="n">
         <v>87322</v>
@@ -2755,19 +2758,20 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>707081</v>
+        <v>707295</v>
       </c>
       <c r="R20" t="n">
-        <v>6635696</v>
+        <v>6635639</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2791,12 +2795,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2811,70 +2825,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113024358</t>
+          <t>https://artportalen.se/Sighting/112801254</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112798700</v>
+        <v>113024358</v>
       </c>
       <c r="B21" t="n">
-        <v>93205</v>
+        <v>87322</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2058</v>
+        <v>1988</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Kryddspindling</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Cortinarius percomis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>707292</v>
+        <v>707081</v>
       </c>
       <c r="R21" t="n">
-        <v>6635701</v>
+        <v>6635696</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2898,22 +2907,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2928,69 +2927,70 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112798700</t>
+          <t>https://artportalen.se/Sighting/113024358</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>82169978</v>
+        <v>112798700</v>
       </c>
       <c r="B22" t="n">
-        <v>96708</v>
+        <v>93205</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>2058</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707433</v>
+        <v>707292</v>
       </c>
       <c r="R22" t="n">
-        <v>6636161</v>
+        <v>6635701</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3014,12 +3014,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,73 +3038,71 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169978</t>
+          <t>https://artportalen.se/Sighting/112798700</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>82170031</v>
+        <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>96437</v>
+        <v>92493</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2667</v>
+        <v>2064</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Skeletocutis kuehneri</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>A.David</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>707494</v>
+        <v>707112</v>
       </c>
       <c r="R23" t="n">
-        <v>6636268</v>
+        <v>6635712</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3121,17 +3129,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På gammal asp.</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3144,30 +3157,49 @@
       <c r="AG23" t="b">
         <v>0</v>
       </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>violticka</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Trichaptum abietinum</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Trichaptum abietinum</t>
+        </is>
+      </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82170031</t>
+          <t>https://artportalen.se/Sighting/137238347</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132227423</v>
+        <v>82169978</v>
       </c>
       <c r="B24" t="n">
-        <v>96501</v>
+        <v>96708</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,37 +3207,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2671</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>707098</v>
+        <v>707433</v>
       </c>
       <c r="R24" t="n">
-        <v>6635735</v>
+        <v>6636161</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3229,12 +3265,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3243,33 +3279,34 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227423</t>
+          <t>https://artportalen.se/Sighting/82169978</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112801334</v>
+        <v>82170031</v>
       </c>
       <c r="B25" t="n">
-        <v>91680</v>
+        <v>96437</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3277,38 +3314,41 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>3215</v>
+        <v>2667</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>707295</v>
+        <v>707494</v>
       </c>
       <c r="R25" t="n">
-        <v>6635639</v>
+        <v>6636268</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3332,22 +3372,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:15</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På gammal asp.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3356,33 +3391,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801334</t>
+          <t>https://artportalen.se/Sighting/82170031</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112801408</v>
+        <v>132227423</v>
       </c>
       <c r="B26" t="n">
-        <v>91680</v>
+        <v>96501</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3390,35 +3426,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>3215</v>
+        <v>2671</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Östra Eka, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>707224</v>
+        <v>707098</v>
       </c>
       <c r="R26" t="n">
-        <v>6635624</v>
+        <v>6635735</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3445,22 +3480,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:19</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,27 +3500,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801408</t>
+          <t>https://artportalen.se/Sighting/132227423</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112800970</v>
+        <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>92497</v>
+        <v>96604</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3503,38 +3528,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3884</v>
+        <v>2809</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>707362</v>
+        <v>707172</v>
       </c>
       <c r="R27" t="n">
-        <v>6635699</v>
+        <v>6635643</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3558,22 +3582,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3588,27 +3612,31 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112800970</t>
+          <t>https://artportalen.se/Sighting/137238314</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>82169956</v>
+        <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92333</v>
+        <v>92357</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3616,40 +3644,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4217</v>
+        <v>3008</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>707409</v>
+        <v>707097</v>
       </c>
       <c r="R28" t="n">
-        <v>6636127</v>
+        <v>6635682</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3673,53 +3698,61 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På barklös tallåga. Fruktkroppen kan eventuellt vara den mer ovanliga och rödlistade laxgröppan.</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF28" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169956</t>
+          <t>https://artportalen.se/Sighting/137238287</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132214935</v>
+        <v>112801334</v>
       </c>
       <c r="B29" t="n">
-        <v>92370</v>
+        <v>91680</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3727,37 +3760,38 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4217</v>
+        <v>3215</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>707044</v>
+        <v>707295</v>
       </c>
       <c r="R29" t="n">
-        <v>6635846</v>
+        <v>6635639</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3781,12 +3815,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3797,21 +3841,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3821,44 +3850,44 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132214935</t>
+          <t>https://artportalen.se/Sighting/112801334</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112800547</v>
+        <v>112801408</v>
       </c>
       <c r="B30" t="n">
-        <v>93189</v>
+        <v>91680</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4361</v>
+        <v>3215</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3869,10 +3898,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>707340</v>
+        <v>707224</v>
       </c>
       <c r="R30" t="n">
-        <v>6635819</v>
+        <v>6635624</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3904,7 +3933,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3914,7 +3943,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3940,55 +3969,54 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112800547</t>
+          <t>https://artportalen.se/Sighting/112801408</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112801723</v>
+        <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>93189</v>
+        <v>92368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4361</v>
+        <v>3298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>707171</v>
+        <v>707185</v>
       </c>
       <c r="R31" t="n">
-        <v>6635473</v>
+        <v>6635715</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4012,22 +4040,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4042,68 +4070,70 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801723</t>
+          <t>https://artportalen.se/Sighting/137238296</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>82170167</v>
+        <v>112800970</v>
       </c>
       <c r="B32" t="n">
-        <v>93197</v>
+        <v>92497</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>3884</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>707527</v>
+        <v>707362</v>
       </c>
       <c r="R32" t="n">
-        <v>6636021</v>
+        <v>6635699</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4127,12 +4157,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4141,82 +4181,74 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82170167</t>
+          <t>https://artportalen.se/Sighting/112800970</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>73253943</v>
+        <v>82169956</v>
       </c>
       <c r="B33" t="n">
-        <v>93209</v>
+        <v>92333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4366</v>
+        <v>4217</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Borg, 450 m NW, Estuna, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>707356</v>
+        <v>707409</v>
       </c>
       <c r="R33" t="n">
-        <v>6635811</v>
+        <v>6636127</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4240,24 +4272,24 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Mossig äldre barrskog. Medobs Edvin Stighäll.</t>
+          <t>På barklös tallåga. Fruktkroppen kan eventuellt vara den mer ovanliga och rödlistade laxgröppan.</t>
         </is>
       </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
@@ -4266,75 +4298,65 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73253943</t>
+          <t>https://artportalen.se/Sighting/82169956</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>73253961</v>
+        <v>132214935</v>
       </c>
       <c r="B34" t="n">
-        <v>93209</v>
+        <v>92370</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4366</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Skrattsjön, S om, Estuna, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>707542</v>
+        <v>707044</v>
       </c>
       <c r="R34" t="n">
-        <v>6636370</v>
+        <v>6635846</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4358,17 +4380,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog, invid mindre stig. Medobs Edvin Stighäll.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4377,56 +4394,70 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73253961</t>
+          <t>https://artportalen.se/Sighting/132214935</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112801234</v>
+        <v>112800547</v>
       </c>
       <c r="B35" t="n">
-        <v>89143</v>
+        <v>93189</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4437,10 +4468,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>707301</v>
+        <v>707340</v>
       </c>
       <c r="R35" t="n">
-        <v>6635643</v>
+        <v>6635819</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4472,7 +4503,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4482,7 +4513,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4508,38 +4539,38 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801234</t>
+          <t>https://artportalen.se/Sighting/112800547</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112801348</v>
+        <v>112801723</v>
       </c>
       <c r="B36" t="n">
-        <v>89143</v>
+        <v>93189</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4405</v>
+        <v>4361</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diskvaxskivling</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hygrophorus discoideus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.) Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4550,10 +4581,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>707295</v>
+        <v>707171</v>
       </c>
       <c r="R36" t="n">
-        <v>6635639</v>
+        <v>6635473</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4585,7 +4616,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4595,7 +4626,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4621,55 +4652,57 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801348</t>
+          <t>https://artportalen.se/Sighting/112801723</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112801220</v>
+        <v>82170167</v>
       </c>
       <c r="B37" t="n">
-        <v>92869</v>
+        <v>93197</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4769</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>707301</v>
+        <v>707527</v>
       </c>
       <c r="R37" t="n">
-        <v>6635640</v>
+        <v>6636021</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4693,22 +4726,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4717,72 +4740,82 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801220</t>
+          <t>https://artportalen.se/Sighting/82170167</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112801302</v>
+        <v>73253943</v>
       </c>
       <c r="B38" t="n">
-        <v>92869</v>
+        <v>93209</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4769</v>
+        <v>4366</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Borg, 450 m NW, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>707295</v>
+        <v>707356</v>
       </c>
       <c r="R38" t="n">
-        <v>6635639</v>
+        <v>6635811</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4806,22 +4839,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>16:14</t>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Mossig äldre barrskog. Medobs Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4830,68 +4858,79 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801302</t>
+          <t>https://artportalen.se/Sighting/73253943</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131431278</v>
+        <v>73253961</v>
       </c>
       <c r="B39" t="n">
-        <v>91966</v>
+        <v>93209</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5321</v>
+        <v>4366</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Haggård, Upl</t>
+          <t>Skrattsjön, S om, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>707150</v>
+        <v>707542</v>
       </c>
       <c r="R39" t="n">
-        <v>6636054</v>
+        <v>6636370</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4918,12 +4957,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog, invid mindre stig. Medobs Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4939,31 +4983,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Aivars Dunskis</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Amelie Lindhagen</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>Värdefull natur i Stockholms län</t>
-        </is>
-      </c>
+          <t>Kristoffer Stighäll</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131431278</t>
+          <t>https://artportalen.se/Sighting/73253961</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132214790</v>
+        <v>112801234</v>
       </c>
       <c r="B40" t="n">
-        <v>92031</v>
+        <v>89143</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4971,37 +5011,38 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5321</v>
+        <v>4405</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>707028</v>
+        <v>707301</v>
       </c>
       <c r="R40" t="n">
-        <v>6635854</v>
+        <v>6635643</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5025,12 +5066,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5050,63 +5101,61 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132214790</t>
+          <t>https://artportalen.se/Sighting/112801234</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>82257709</v>
+        <v>112801348</v>
       </c>
       <c r="B41" t="n">
-        <v>91930</v>
+        <v>89143</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5442</v>
+        <v>4405</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Diskvaxskivling</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hygrophorus discoideus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.) Fr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>707453</v>
+        <v>707295</v>
       </c>
       <c r="R41" t="n">
-        <v>6635868</v>
+        <v>6635639</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5130,12 +5179,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5144,69 +5203,69 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82257709</t>
+          <t>https://artportalen.se/Sighting/112801348</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132216648</v>
+        <v>112801220</v>
       </c>
       <c r="B42" t="n">
-        <v>91995</v>
+        <v>92869</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5442</v>
+        <v>4769</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>707065</v>
+        <v>707301</v>
       </c>
       <c r="R42" t="n">
-        <v>6635643</v>
+        <v>6635640</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5233,12 +5292,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5258,22 +5327,22 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132216648</t>
+          <t>https://artportalen.se/Sighting/112801220</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>82169875</v>
+        <v>112801302</v>
       </c>
       <c r="B43" t="n">
-        <v>91872</v>
+        <v>92869</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5281,40 +5350,38 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>707315</v>
+        <v>707295</v>
       </c>
       <c r="R43" t="n">
-        <v>6635985</v>
+        <v>6635639</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5338,17 +5405,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På torrgran.</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5357,34 +5429,33 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169875</t>
+          <t>https://artportalen.se/Sighting/112801302</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>82257673</v>
+        <v>131431278</v>
       </c>
       <c r="B44" t="n">
-        <v>91872</v>
+        <v>91966</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5392,40 +5463,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Haggård, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>707522</v>
+        <v>707150</v>
       </c>
       <c r="R44" t="n">
-        <v>6635935</v>
+        <v>6636054</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5449,17 +5517,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>2024-09-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5475,27 +5538,31 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Aivars Dunskis</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr">
+        <is>
+          <t>Värdefull natur i Stockholms län</t>
+        </is>
+      </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82257673</t>
+          <t>https://artportalen.se/Sighting/131431278</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>82257697</v>
+        <v>132214790</v>
       </c>
       <c r="B45" t="n">
-        <v>91872</v>
+        <v>92031</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5503,40 +5570,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>5321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>707468</v>
+        <v>707028</v>
       </c>
       <c r="R45" t="n">
-        <v>6635878</v>
+        <v>6635854</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5560,17 +5624,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5579,72 +5638,74 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82257697</t>
+          <t>https://artportalen.se/Sighting/132214790</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>132217832</v>
+        <v>82257709</v>
       </c>
       <c r="B46" t="n">
-        <v>91937</v>
+        <v>91930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>707382</v>
+        <v>707453</v>
       </c>
       <c r="R46" t="n">
-        <v>6635863</v>
+        <v>6635868</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5668,12 +5729,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5682,71 +5743,69 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132217832</t>
+          <t>https://artportalen.se/Sighting/82257709</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112813338</v>
+        <v>132216648</v>
       </c>
       <c r="B47" t="n">
-        <v>91435</v>
+        <v>91995</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5747</v>
+        <v>5442</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Läderdoftande fingersvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ramaria safraniolens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Christan</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>707218</v>
+        <v>707065</v>
       </c>
       <c r="R47" t="n">
-        <v>6635565</v>
+        <v>6635643</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5773,27 +5832,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Luktar starkt "skoaffär". Växte intill grov gran.</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5802,7 +5846,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5814,70 +5857,63 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112813338</t>
+          <t>https://artportalen.se/Sighting/132216648</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>73253929</v>
+        <v>82169875</v>
       </c>
       <c r="B48" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Borg, 400 m WNW, Estuna, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>707314</v>
+        <v>707315</v>
       </c>
       <c r="R48" t="n">
-        <v>6635657</v>
+        <v>6635985</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5901,17 +5937,17 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2018-09-23</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>S stigen. Mossrik äldre barrskog. Medobs Edvin Stighäll.</t>
+          <t>På torrgran.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5927,49 +5963,49 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristoffer Stighäll</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73253929</t>
+          <t>https://artportalen.se/Sighting/82169875</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>82169803</v>
+        <v>82257673</v>
       </c>
       <c r="B49" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5982,10 +6018,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>707351</v>
+        <v>707522</v>
       </c>
       <c r="R49" t="n">
-        <v>6635947</v>
+        <v>6635935</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6020,6 +6056,11 @@
           <t>2020-02-12</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6044,55 +6085,57 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169803</t>
+          <t>https://artportalen.se/Sighting/82257673</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112798925</v>
+        <v>82257697</v>
       </c>
       <c r="B50" t="n">
-        <v>93233</v>
+        <v>91872</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>707356</v>
+        <v>707468</v>
       </c>
       <c r="R50" t="n">
-        <v>6635721</v>
+        <v>6635878</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6116,22 +6159,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>15:01</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6140,72 +6178,72 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112798925</t>
+          <t>https://artportalen.se/Sighting/82257697</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112800935</v>
+        <v>132217832</v>
       </c>
       <c r="B51" t="n">
-        <v>93233</v>
+        <v>91937</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>707362</v>
+        <v>707382</v>
       </c>
       <c r="R51" t="n">
-        <v>6635739</v>
+        <v>6635863</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6229,22 +6267,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>15:57</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6264,61 +6292,60 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112800935</t>
+          <t>https://artportalen.se/Sighting/132217832</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112800985</v>
+        <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>93233</v>
+        <v>92106</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5964</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>707359</v>
+        <v>707034</v>
       </c>
       <c r="R52" t="n">
-        <v>6635714</v>
+        <v>6635830</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6342,22 +6369,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6372,63 +6399,69 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112800985</t>
+          <t>https://artportalen.se/Sighting/137238275</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112801385</v>
+        <v>112813338</v>
       </c>
       <c r="B53" t="n">
-        <v>93233</v>
+        <v>91435</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5964</v>
+        <v>5747</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Läderdoftande fingersvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria safraniolens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Christan</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>707244</v>
+        <v>707218</v>
       </c>
       <c r="R53" t="n">
-        <v>6635642</v>
+        <v>6635565</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6460,7 +6493,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6470,7 +6503,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Luktar starkt "skoaffär". Växte intill grov gran.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6479,6 +6517,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6496,13 +6535,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801385</t>
+          <t>https://artportalen.se/Sighting/112813338</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112801678</v>
+        <v>73253929</v>
       </c>
       <c r="B54" t="n">
         <v>93233</v>
@@ -6530,21 +6569,30 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ekalund, Ekalund, Upl</t>
+          <t>Borg, 400 m WNW, Estuna, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>707208</v>
+        <v>707314</v>
       </c>
       <c r="R54" t="n">
-        <v>6635529</v>
+        <v>6635657</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6568,22 +6616,17 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2018-09-23</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2023-10-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:31</t>
+          <t>2018-09-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>S stigen. Mossrik äldre barrskog. Medobs Edvin Stighäll.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6592,30 +6635,31 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Kristoffer Stighäll</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112801678</t>
+          <t>https://artportalen.se/Sighting/73253929</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>113024361</v>
+        <v>82169803</v>
       </c>
       <c r="B55" t="n">
         <v>93233</v>
@@ -6644,19 +6688,22 @@
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>707207</v>
+        <v>707351</v>
       </c>
       <c r="R55" t="n">
-        <v>6635607</v>
+        <v>6635947</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6680,12 +6727,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6701,31 +6748,27 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY55" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113024361</t>
+          <t>https://artportalen.se/Sighting/82169803</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>113024364</v>
+        <v>112798925</v>
       </c>
       <c r="B56" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6733,37 +6776,38 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>707080</v>
+        <v>707356</v>
       </c>
       <c r="R56" t="n">
-        <v>6635593</v>
+        <v>6635721</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6787,12 +6831,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6807,31 +6861,27 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY56" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113024364</t>
+          <t>https://artportalen.se/Sighting/112798925</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>113024365</v>
+        <v>112800935</v>
       </c>
       <c r="B57" t="n">
-        <v>93235</v>
+        <v>93233</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6839,37 +6889,38 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5966</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>707115</v>
+        <v>707362</v>
       </c>
       <c r="R57" t="n">
-        <v>6635591</v>
+        <v>6635739</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6893,12 +6944,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2023-10-24</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6913,72 +6974,66 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY57" t="inlineStr">
-        <is>
-          <t>Svampar i Roslagen</t>
-        </is>
-      </c>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113024365</t>
+          <t>https://artportalen.se/Sighting/112800935</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>82169853</v>
+        <v>112800985</v>
       </c>
       <c r="B58" t="n">
-        <v>83290</v>
+        <v>93233</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6439</v>
+        <v>5964</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>707322</v>
+        <v>707359</v>
       </c>
       <c r="R58" t="n">
-        <v>6635990</v>
+        <v>6635714</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7002,17 +7057,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>På högstubbe av asp.</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7021,34 +7081,33 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169853</t>
+          <t>https://artportalen.se/Sighting/112800985</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>82169931</v>
+        <v>112801385</v>
       </c>
       <c r="B59" t="n">
-        <v>79946</v>
+        <v>93233</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7056,40 +7115,38 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>5964</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>707383</v>
+        <v>707244</v>
       </c>
       <c r="R59" t="n">
-        <v>6636007</v>
+        <v>6635642</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7113,17 +7170,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>På gammal tallstubbe.</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7132,80 +7194,72 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169931</t>
+          <t>https://artportalen.se/Sighting/112801385</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>82169643</v>
+        <v>112801678</v>
       </c>
       <c r="B60" t="n">
-        <v>57950</v>
+        <v>93233</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>707161</v>
+        <v>707208</v>
       </c>
       <c r="R60" t="n">
-        <v>6636002</v>
+        <v>6635529</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7229,12 +7283,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7249,73 +7313,65 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169643</t>
+          <t>https://artportalen.se/Sighting/112801678</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>132243945</v>
+        <v>113024361</v>
       </c>
       <c r="B61" t="n">
-        <v>57972</v>
+        <v>93233</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>5964</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>707094</v>
+        <v>707207</v>
       </c>
       <c r="R61" t="n">
-        <v>6635643</v>
+        <v>6635607</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7339,27 +7395,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7368,100 +7409,85 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>vanlig gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Picea abies subsp. abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132243945</t>
+          <t>https://artportalen.se/Sighting/113024361</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>82169652</v>
+        <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>5179</v>
+        <v>93477</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100526</v>
+        <v>5964</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>SO Haggård 10 okt, Upl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>707161</v>
+        <v>707271</v>
       </c>
       <c r="R62" t="n">
-        <v>6636002</v>
+        <v>6635675</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7485,17 +7511,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gnagspår på torrgran.</t>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7504,81 +7535,75 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Irena Koelemeijer</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY62" t="inlineStr"/>
+          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>Upplands kalkbarrskogar</t>
+        </is>
+      </c>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169652</t>
+          <t>https://artportalen.se/Sighting/137238301</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>82169771</v>
+        <v>113024364</v>
       </c>
       <c r="B63" t="n">
-        <v>5179</v>
+        <v>93235</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>707269</v>
+        <v>707080</v>
       </c>
       <c r="R63" t="n">
-        <v>6635917</v>
+        <v>6635593</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7602,12 +7627,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7616,77 +7641,75 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY63" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169771</t>
+          <t>https://artportalen.se/Sighting/113024364</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132216358</v>
+        <v>113024365</v>
       </c>
       <c r="B64" t="n">
-        <v>5181</v>
+        <v>93235</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>707052</v>
+        <v>707115</v>
       </c>
       <c r="R64" t="n">
-        <v>6635680</v>
+        <v>6635591</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7710,12 +7733,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2023-10-24</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7730,27 +7753,31 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
-        </is>
-      </c>
-      <c r="AY64" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>Svampar i Roslagen</t>
+        </is>
+      </c>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132216358</t>
+          <t>https://artportalen.se/Sighting/113024365</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>82169826</v>
+        <v>82169853</v>
       </c>
       <c r="B65" t="n">
-        <v>5471</v>
+        <v>83290</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7758,32 +7785,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>101377</v>
+        <v>6439</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stekelbock</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Necydalis major</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7831,7 +7852,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Gnagspår på högstubbe av asp.</t>
+          <t>På högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7858,49 +7879,43 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169826</t>
+          <t>https://artportalen.se/Sighting/82169853</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>82169409</v>
+        <v>82169931</v>
       </c>
       <c r="B66" t="n">
-        <v>4872</v>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>101675</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Aspvedgnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ptilinus fuscus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Geoffroy, 1785)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -7908,10 +7923,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>707123</v>
+        <v>707383</v>
       </c>
       <c r="R66" t="n">
-        <v>6635931</v>
+        <v>6636007</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -7948,7 +7963,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Gnagspår på högstubbe av asp.</t>
+          <t>På gammal tallstubbe.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7975,16 +7990,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169409</t>
+          <t>https://artportalen.se/Sighting/82169931</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>82169013</v>
+        <v>82169643</v>
       </c>
       <c r="B67" t="n">
-        <v>4781</v>
+        <v>57950</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7992,30 +8007,29 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
@@ -8025,10 +8039,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>707090</v>
+        <v>707161</v>
       </c>
       <c r="R67" t="n">
-        <v>6635941</v>
+        <v>6636002</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8069,7 +8083,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -8081,22 +8094,22 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169013</t>
+          <t>https://artportalen.se/Sighting/82169643</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>82169550</v>
+        <v>132243945</v>
       </c>
       <c r="B68" t="n">
-        <v>4781</v>
+        <v>57972</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8104,30 +8117,29 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>102306</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -8137,10 +8149,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>707170</v>
+        <v>707094</v>
       </c>
       <c r="R68" t="n">
-        <v>6635990</v>
+        <v>6635643</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8167,12 +8179,27 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska hack och barkflagningar på gran. Fanns även på flera ställen i denna skog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8181,34 +8208,53 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>vanlig gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Picea abies subsp. abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169550</t>
+          <t>https://artportalen.se/Sighting/132243945</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>82169571</v>
+        <v>82169652</v>
       </c>
       <c r="B69" t="n">
-        <v>4781</v>
+        <v>5179</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8216,21 +8262,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8249,10 +8295,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>707199</v>
+        <v>707161</v>
       </c>
       <c r="R69" t="n">
-        <v>6635984</v>
+        <v>6636002</v>
       </c>
       <c r="S69" t="n">
         <v>5</v>
@@ -8287,6 +8333,11 @@
           <t>2020-02-12</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Gnagspår på torrgran.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8311,16 +8362,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169571</t>
+          <t>https://artportalen.se/Sighting/82169652</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>82169734</v>
+        <v>82169771</v>
       </c>
       <c r="B70" t="n">
-        <v>4781</v>
+        <v>5179</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8328,21 +8379,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102306</v>
+        <v>100526</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8361,10 +8412,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>707226</v>
+        <v>707269</v>
       </c>
       <c r="R70" t="n">
-        <v>6635935</v>
+        <v>6635917</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8423,63 +8474,59 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169734</t>
+          <t>https://artportalen.se/Sighting/82169771</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>132243952</v>
+        <v>132216358</v>
       </c>
       <c r="B71" t="n">
-        <v>58519</v>
+        <v>5181</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102990</v>
+        <v>100526</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>707009</v>
+        <v>707052</v>
       </c>
       <c r="R71" t="n">
-        <v>6635864</v>
+        <v>6635680</v>
       </c>
       <c r="S71" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8506,21 +8553,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8529,36 +8566,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132243952</t>
+          <t>https://artportalen.se/Sighting/132216358</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>132243953</v>
+        <v>82169826</v>
       </c>
       <c r="B72" t="n">
-        <v>58349</v>
+        <v>5471</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8566,46 +8598,46 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>103015</v>
+        <v>101377</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stekelbock</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Necydalis major</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>707009</v>
+        <v>707322</v>
       </c>
       <c r="R72" t="n">
-        <v>6635864</v>
+        <v>6635990</v>
       </c>
       <c r="S72" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8629,22 +8661,17 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>11:20</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>14:07</t>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Gnagspår på högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8653,92 +8680,81 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132243953</t>
+          <t>https://artportalen.se/Sighting/82169826</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125656453</v>
+        <v>82169409</v>
       </c>
       <c r="B73" t="n">
-        <v>58114</v>
+        <v>4872</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>103021</v>
+        <v>101675</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Aspvedgnagare</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ptilinus fuscus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Geoffroy, 1785)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>bo, hörda ungar</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Skrattsjön SV, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>707472</v>
+        <v>707123</v>
       </c>
       <c r="R73" t="n">
-        <v>6636313</v>
+        <v>6635931</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8762,17 +8778,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Matar ungar ca 200 m V</t>
+          <t>Gnagspår på högstubbe av asp.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8781,33 +8797,34 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Eriksson</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Eriksson</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125656453</t>
+          <t>https://artportalen.se/Sighting/82169409</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>82169778</v>
+        <v>82169013</v>
       </c>
       <c r="B74" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8815,21 +8832,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8848,10 +8865,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>707269</v>
+        <v>707090</v>
       </c>
       <c r="R74" t="n">
-        <v>6635917</v>
+        <v>6635941</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8904,22 +8921,22 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82169778</t>
+          <t>https://artportalen.se/Sighting/82169013</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>132216402</v>
+        <v>82169550</v>
       </c>
       <c r="B75" t="n">
-        <v>107690</v>
+        <v>4781</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8927,37 +8944,46 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>219686</v>
+        <v>102306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vätteros</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lathraea squamaria</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>707053</v>
+        <v>707170</v>
       </c>
       <c r="R75" t="n">
-        <v>6635668</v>
+        <v>6635990</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8981,12 +9007,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8995,33 +9021,34 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132216402</t>
+          <t>https://artportalen.se/Sighting/82169550</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>132215849</v>
+        <v>82169571</v>
       </c>
       <c r="B76" t="n">
-        <v>99218</v>
+        <v>4781</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9029,37 +9056,46 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>219862</v>
+        <v>102306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Fisingsberget, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>707074</v>
+        <v>707199</v>
       </c>
       <c r="R76" t="n">
-        <v>6635682</v>
+        <v>6635984</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9083,12 +9119,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9097,33 +9133,34 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132215849</t>
+          <t>https://artportalen.se/Sighting/82169571</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>132227426</v>
+        <v>82169734</v>
       </c>
       <c r="B77" t="n">
-        <v>99218</v>
+        <v>4781</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9131,37 +9168,46 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>219862</v>
+        <v>102306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>707352</v>
+        <v>707226</v>
       </c>
       <c r="R77" t="n">
-        <v>6635802</v>
+        <v>6635935</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9185,12 +9231,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9199,55 +9245,56 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227426</t>
+          <t>https://artportalen.se/Sighting/82169734</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>132243950</v>
+        <v>132243952</v>
       </c>
       <c r="B78" t="n">
-        <v>99218</v>
+        <v>58519</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>219862</v>
+        <v>102990</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Nästrot</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Neottia nidus-avis</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -9255,14 +9302,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9271,13 +9313,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>707098</v>
+        <v>707009</v>
       </c>
       <c r="R78" t="n">
-        <v>6635691</v>
+        <v>6635864</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9347,16 +9389,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132243950</t>
+          <t>https://artportalen.se/Sighting/132243952</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>132222629</v>
+        <v>132243953</v>
       </c>
       <c r="B79" t="n">
-        <v>106324</v>
+        <v>58349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9364,49 +9406,46 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>707139</v>
+        <v>707009</v>
       </c>
       <c r="R79" t="n">
-        <v>6635834</v>
+        <v>6635864</v>
       </c>
       <c r="S79" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9433,14 +9472,19 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>C:a 10 exemplar.</t>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9449,89 +9493,89 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132222629</t>
+          <t>https://artportalen.se/Sighting/132243953</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>132222660</v>
+        <v>125656453</v>
       </c>
       <c r="B80" t="n">
-        <v>106324</v>
+        <v>58114</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>bo, hörda ungar</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Östra Eka SO om, Upl</t>
+          <t>Skrattsjön SV, Upl</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>707127</v>
+        <v>707472</v>
       </c>
       <c r="R80" t="n">
-        <v>6635639</v>
+        <v>6636313</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -9558,17 +9602,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2025-06-03</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>C:a 10 ex.</t>
+          <t>Matar ungar ca 200 m V</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9577,34 +9621,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Anders Eriksson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gabriel Ekman</t>
+          <t>Anders Eriksson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132222660</t>
+          <t>https://artportalen.se/Sighting/125656453</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>132214164</v>
+        <v>82169778</v>
       </c>
       <c r="B81" t="n">
-        <v>106679</v>
+        <v>5199</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9612,37 +9655,46 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221570</v>
+        <v>105930</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk lungört</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pulmonaria obscura</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Dumort.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>706914</v>
+        <v>707269</v>
       </c>
       <c r="R81" t="n">
-        <v>6635923</v>
+        <v>6635917</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9666,12 +9718,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2020-02-12</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9680,33 +9732,34 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Bo Törnquist</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132214164</t>
+          <t>https://artportalen.se/Sighting/82169778</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>132218069</v>
+        <v>132216402</v>
       </c>
       <c r="B82" t="n">
-        <v>98060</v>
+        <v>107690</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9714,16 +9767,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>219686</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vätteros</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lathraea squamaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9734,17 +9787,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Borg, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>707184</v>
+        <v>707053</v>
       </c>
       <c r="R82" t="n">
-        <v>6635847</v>
+        <v>6635668</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9799,16 +9852,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132218069</t>
+          <t>https://artportalen.se/Sighting/132216402</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>132214156</v>
+        <v>132215849</v>
       </c>
       <c r="B83" t="n">
-        <v>104707</v>
+        <v>99218</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9816,34 +9869,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Fisingsberget, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706914</v>
+        <v>707074</v>
       </c>
       <c r="R83" t="n">
-        <v>6635923</v>
+        <v>6635682</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9901,16 +9954,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132214156</t>
+          <t>https://artportalen.se/Sighting/132215849</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132227419</v>
+        <v>132227426</v>
       </c>
       <c r="B84" t="n">
-        <v>104707</v>
+        <v>99218</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9918,21 +9971,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222412</v>
+        <v>219862</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9942,10 +9995,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>706917</v>
+        <v>707352</v>
       </c>
       <c r="R84" t="n">
-        <v>6635908</v>
+        <v>6635802</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10003,16 +10056,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227419</t>
+          <t>https://artportalen.se/Sighting/132227426</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>82170052</v>
+        <v>132243950</v>
       </c>
       <c r="B85" t="n">
-        <v>101326</v>
+        <v>99218</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10020,38 +10073,48 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222498</v>
+        <v>219862</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Nästrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia nidus-avis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Östra Eka, SO om, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>707513</v>
+        <v>707098</v>
       </c>
       <c r="R85" t="n">
-        <v>6636298</v>
+        <v>6635691</v>
       </c>
       <c r="S85" t="n">
         <v>5</v>
@@ -10078,12 +10141,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2020-02-12</t>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>14:07</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10092,67 +10165,88 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Bo Törnquist</t>
+          <t>Joakim Ekman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82170052</t>
+          <t>https://artportalen.se/Sighting/132243950</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>132214236</v>
+        <v>132222629</v>
       </c>
       <c r="B86" t="n">
-        <v>80703</v>
+        <v>106324</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228430</v>
+        <v>221144</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>706939</v>
+        <v>707139</v>
       </c>
       <c r="R86" t="n">
-        <v>6635897</v>
+        <v>6635834</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10184,72 +10278,103 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>C:a 10 exemplar.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132214236</t>
+          <t>https://artportalen.se/Sighting/132222629</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>132218153</v>
+        <v>132222660</v>
       </c>
       <c r="B87" t="n">
-        <v>80703</v>
+        <v>106324</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228430</v>
+        <v>221144</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ekalund, Upl</t>
+          <t>Östra Eka SO om, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>707015</v>
+        <v>707127</v>
       </c>
       <c r="R87" t="n">
-        <v>6635968</v>
+        <v>6635639</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10281,75 +10406,83 @@
           <t>2026-04-06</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>C:a 10 ex.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Viktor Lund</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132218153</t>
+          <t>https://artportalen.se/Sighting/132222660</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>132243957</v>
+        <v>132214164</v>
       </c>
       <c r="B88" t="n">
-        <v>80703</v>
+        <v>106679</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228430</v>
+        <v>221570</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Mörk lungört</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Blastenia relicta</t>
+          <t>Pulmonaria obscura</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Arup &amp; Vondrák</t>
+          <t>Dumort.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>706941</v>
+        <v>706914</v>
       </c>
       <c r="R88" t="n">
-        <v>6635897</v>
+        <v>6635923</v>
       </c>
       <c r="S88" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10376,85 +10509,44 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På en klen aspgren på en stor asplåga.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Död gren</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Dead branch  # Populus tremula</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132243957</t>
+          <t>https://artportalen.se/Sighting/132214164</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>132227420</v>
+        <v>132218069</v>
       </c>
       <c r="B89" t="n">
-        <v>80438</v>
+        <v>98060</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10462,37 +10554,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229497</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Östra Eka, Upl</t>
+          <t>Borg, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>707005</v>
+        <v>707184</v>
       </c>
       <c r="R89" t="n">
-        <v>6635885</v>
+        <v>6635847</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10536,27 +10628,27 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Cajsa Björkén</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132227420</t>
+          <t>https://artportalen.se/Sighting/132218069</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132243955</v>
+        <v>132214156</v>
       </c>
       <c r="B90" t="n">
-        <v>80438</v>
+        <v>104707</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10564,37 +10656,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229497</v>
+        <v>222412</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Östra Eka, SO om, Upl</t>
+          <t>Ekalund, Upl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>707009</v>
+        <v>706914</v>
       </c>
       <c r="R90" t="n">
-        <v>6635864</v>
+        <v>6635923</v>
       </c>
       <c r="S90" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10621,21 +10713,11 @@
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>11:20</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>14:07</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10644,25 +10726,783 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>Barrblandskog, luckig</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Joakim Ekman</t>
+          <t>Viktor Lund</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214156</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132227419</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>706917</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6635908</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227419</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>82170052</v>
+      </c>
+      <c r="B92" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>707513</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6636298</v>
+      </c>
+      <c r="S92" t="n">
+        <v>5</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2020-02-12</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Bo Törnquist</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Bo Törnquist, Kjell  Andersson, Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82170052</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132214236</v>
+      </c>
+      <c r="B93" t="n">
+        <v>80703</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ekalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>706939</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6635897</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132214236</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>132218153</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80703</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ekalund, Upl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>707015</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6635968</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Cajsa Björkén, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132218153</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>132243957</v>
+      </c>
+      <c r="B95" t="n">
+        <v>80703</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228430</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Blastenia relicta</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Arup &amp; Vondrák</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>706941</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6635897</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>På en klen aspgren på en stor asplåga.</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Dead branch  # Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132243957</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>132227420</v>
+      </c>
+      <c r="B96" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Östra Eka, Upl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>707005</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6635885</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Cajsa Björkén, Viktor Lund, Martin Westberg, Joakim Ekman, Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132227420</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>132243955</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Östra Eka, SO om, Upl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>707009</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6635864</v>
+      </c>
+      <c r="S97" t="n">
+        <v>5</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Estuna</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Barrblandskog, luckig</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Joakim Ekman</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Joakim Ekman, Gabriel Ekman, Viktor Lund, Cajsa Björkén, Martin Westberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132243955</t>
         </is>
@@ -10759,6 +11599,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92817</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2540,6 +2540,8 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>SO Haggård 10 okt, Upl</t>
@@ -2600,6 +2602,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2611,7 +2614,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -3064,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92493</v>
+        <v>92495</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3180,7 +3183,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -3520,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96604</v>
+        <v>96606</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3617,7 +3620,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
@@ -3636,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3662,6 +3665,9 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>SO Haggård 10 okt, Upl</t>
@@ -3722,6 +3728,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3733,7 +3740,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
@@ -3978,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,6 +4011,9 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>SO Haggård 10 okt, Upl</t>
@@ -4064,6 +4074,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4075,7 +4086,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
@@ -6307,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6404,7 +6415,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
@@ -7440,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7475,6 +7486,8 @@
           <t>mycel</t>
         </is>
       </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>SO Haggård 10 okt, Upl</t>
@@ -7535,6 +7548,7 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
@@ -7546,7 +7560,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Irena Koelemeijer, Anders Forsberg, Alexander Hoffmann, Ebba Ganslandt</t>
+          <t>Irena Koelemeijer, Alexander Hoffmann, Ebba Ganslandt, Anders Forsberg</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr">

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92495</v>
+        <v>92498</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96606</v>
+        <v>96609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92359</v>
+        <v>92362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92832</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92498</v>
+        <v>92508</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96609</v>
+        <v>96619</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92362</v>
+        <v>92372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92832</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92508</v>
+        <v>92509</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96619</v>
+        <v>96620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92509</v>
+        <v>92512</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96620</v>
+        <v>96625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92373</v>
+        <v>92376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92838</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92512</v>
+        <v>92514</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96625</v>
+        <v>96627</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92376</v>
+        <v>92378</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92838</v>
+        <v>92843</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92514</v>
+        <v>92519</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96627</v>
+        <v>96633</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92378</v>
+        <v>92383</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92843</v>
+        <v>92855</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92519</v>
+        <v>92531</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96633</v>
+        <v>96645</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92383</v>
+        <v>92395</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92855</v>
+        <v>92856</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92531</v>
+        <v>92532</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96645</v>
+        <v>96646</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92395</v>
+        <v>92396</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92856</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92532</v>
+        <v>92535</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96646</v>
+        <v>96649</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92396</v>
+        <v>92399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>

--- a/artfynd/A 16696-2026 artfynd.xlsx
+++ b/artfynd/A 16696-2026 artfynd.xlsx
@@ -2514,7 +2514,7 @@
         <v>137238304</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         <v>137238347</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3523,7 +3523,7 @@
         <v>137238314</v>
       </c>
       <c r="B27" t="n">
-        <v>96649</v>
+        <v>96653</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3639,7 +3639,7 @@
         <v>137238287</v>
       </c>
       <c r="B28" t="n">
-        <v>92399</v>
+        <v>92403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>137238296</v>
       </c>
       <c r="B31" t="n">
-        <v>92410</v>
+        <v>92414</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -6318,7 +6318,7 @@
         <v>137238275</v>
       </c>
       <c r="B52" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>137238301</v>
       </c>
       <c r="B62" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
